--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2070-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2070-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CED75E2-302D-4154-9DEB-4CB7F15B93B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09D0C055-C00C-40E5-86CB-CA1EDCD3137F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{F6D4F754-5B1C-4326-BAA4-EC463D6AA6E9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E10F2267-98C0-4EE2-91EE-5CD566326D0A}"/>
   </bookViews>
   <sheets>
     <sheet name="2070-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1469,19 +1469,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB85D98C-EDDD-4F39-A116-761135D24CE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD9A6BB-5CCF-4BB8-B056-61CFE68FA2BB}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1635,7 +1635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2020</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="38">
         <v>2019</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2018</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2017</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2016</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
         <v>41</v>
       </c>
